--- a/research_materials/03_results/serving_precision.xlsx
+++ b/research_materials/03_results/serving_precision.xlsx
@@ -459,7 +459,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Built: 2026-10-06 23:35 by src/build_research_materials.py</t>
+          <t>Built: 2026-10-07 02:02 by src/build_research_materials.py</t>
         </is>
       </c>
     </row>
@@ -647,16 +647,30 @@
       <c r="I2" s="3" t="n">
         <v>0.569</v>
       </c>
-      <c r="J2" s="3" t="n"/>
-      <c r="K2" s="3" t="n"/>
-      <c r="L2" s="3" t="n"/>
-      <c r="M2" s="3" t="n"/>
-      <c r="N2" s="3" t="n"/>
-      <c r="O2" s="3" t="n"/>
+      <c r="J2" s="3" t="n">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>-0.026</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.007</v>
+      </c>
       <c r="P2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="3" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -702,16 +716,30 @@
       <c r="I3" s="3" t="n">
         <v>0.363</v>
       </c>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="n"/>
-      <c r="L3" s="3" t="n"/>
-      <c r="M3" s="3" t="n"/>
-      <c r="N3" s="3" t="n"/>
-      <c r="O3" s="3" t="n"/>
+      <c r="J3" s="3" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>-0.024</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.023</v>
+      </c>
       <c r="P3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -826,16 +854,30 @@
       <c r="I5" s="3" t="n">
         <v>0.575</v>
       </c>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="n"/>
-      <c r="L5" s="3" t="n"/>
-      <c r="M5" s="3" t="n"/>
-      <c r="N5" s="3" t="n"/>
-      <c r="O5" s="3" t="n"/>
+      <c r="J5" s="3" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>-0.008999999999999999</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>-0.043</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.031</v>
+      </c>
       <c r="P5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -881,16 +923,30 @@
       <c r="I6" s="3" t="n">
         <v>0.333</v>
       </c>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="3" t="n"/>
-      <c r="L6" s="3" t="n"/>
-      <c r="M6" s="3" t="n"/>
-      <c r="N6" s="3" t="n"/>
-      <c r="O6" s="3" t="n"/>
+      <c r="J6" s="3" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>-0.031</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.008</v>
+      </c>
       <c r="P6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1005,16 +1061,30 @@
       <c r="I8" s="3" t="n">
         <v>0.5570000000000001</v>
       </c>
-      <c r="J8" s="3" t="n"/>
-      <c r="K8" s="3" t="n"/>
-      <c r="L8" s="3" t="n"/>
-      <c r="M8" s="3" t="n"/>
-      <c r="N8" s="3" t="n"/>
-      <c r="O8" s="3" t="n"/>
+      <c r="J8" s="3" t="n">
+        <v>0.544</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>-0.037</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.047</v>
+      </c>
       <c r="P8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1060,16 +1130,30 @@
       <c r="I9" s="3" t="n">
         <v>0.372</v>
       </c>
-      <c r="J9" s="3" t="n"/>
-      <c r="K9" s="3" t="n"/>
-      <c r="L9" s="3" t="n"/>
-      <c r="M9" s="3" t="n"/>
-      <c r="N9" s="3" t="n"/>
-      <c r="O9" s="3" t="n"/>
+      <c r="J9" s="3" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>-0.014</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>0.022</v>
+      </c>
       <c r="P9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1184,16 +1268,30 @@
       <c r="I11" s="3" t="n">
         <v>0.499</v>
       </c>
-      <c r="J11" s="3" t="n"/>
-      <c r="K11" s="3" t="n"/>
-      <c r="L11" s="3" t="n"/>
-      <c r="M11" s="3" t="n"/>
-      <c r="N11" s="3" t="n"/>
-      <c r="O11" s="3" t="n"/>
+      <c r="J11" s="3" t="n">
+        <v>0.482</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>-0.017</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>-0.039</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>-0.062</v>
+      </c>
       <c r="P11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1239,16 +1337,30 @@
       <c r="I12" s="3" t="n">
         <v>0.323</v>
       </c>
-      <c r="J12" s="3" t="n"/>
-      <c r="K12" s="3" t="n"/>
-      <c r="L12" s="3" t="n"/>
-      <c r="M12" s="3" t="n"/>
-      <c r="N12" s="3" t="n"/>
-      <c r="O12" s="3" t="n"/>
+      <c r="J12" s="3" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>-0.016</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>0.749</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>0.014</v>
+      </c>
       <c r="P12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q12" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1868,7 +1980,7 @@
         <v>500</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>0.228</v>
+        <v>0.541</v>
       </c>
     </row>
     <row r="22">
@@ -2075,7 +2187,7 @@
         <v>500</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>0.056</v>
+        <v>0.128</v>
       </c>
     </row>
     <row r="25">
@@ -2213,7 +2325,7 @@
         <v>500</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>0.018</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="27">
@@ -2282,7 +2394,7 @@
         <v>500</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>0.018</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="28">
@@ -2420,7 +2532,7 @@
         <v>279</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2834,7 +2946,7 @@
         <v>500</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>0.148</v>
+        <v>0.341</v>
       </c>
     </row>
     <row r="36">
@@ -2903,7 +3015,7 @@
         <v>500</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.6929999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -3041,7 +3153,7 @@
         <v>500</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>0.018</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="39">
@@ -3110,7 +3222,7 @@
         <v>500</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>0.018</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="40">
@@ -3455,7 +3567,7 @@
         <v>499</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.192</v>
       </c>
     </row>
     <row r="45">
@@ -3662,7 +3774,7 @@
         <v>499</v>
       </c>
       <c r="Q47" s="3" t="n">
-        <v>0.058</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="48">
@@ -3731,7 +3843,7 @@
         <v>500</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.081</v>
+        <v>0.189</v>
       </c>
     </row>
     <row r="49">
@@ -3847,16 +3959,30 @@
       <c r="I50" s="3" t="n">
         <v>0.546</v>
       </c>
-      <c r="J50" s="3" t="n"/>
-      <c r="K50" s="3" t="n"/>
-      <c r="L50" s="3" t="n"/>
-      <c r="M50" s="3" t="n"/>
-      <c r="N50" s="3" t="n"/>
-      <c r="O50" s="3" t="n"/>
+      <c r="J50" s="3" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="K50" s="3" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="M50" s="3" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="N50" s="3" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="O50" s="3" t="n">
+        <v>0.044</v>
+      </c>
       <c r="P50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="3" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="Q50" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3902,16 +4028,30 @@
       <c r="I51" s="3" t="n">
         <v>0.361</v>
       </c>
-      <c r="J51" s="3" t="n"/>
-      <c r="K51" s="3" t="n"/>
-      <c r="L51" s="3" t="n"/>
-      <c r="M51" s="3" t="n"/>
-      <c r="N51" s="3" t="n"/>
-      <c r="O51" s="3" t="n"/>
+      <c r="J51" s="3" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="K51" s="3" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="L51" s="3" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="M51" s="3" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="N51" s="3" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="O51" s="3" t="n">
+        <v>0.066</v>
+      </c>
       <c r="P51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q51" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -4026,16 +4166,30 @@
       <c r="I53" s="3" t="n">
         <v>0.5610000000000001</v>
       </c>
-      <c r="J53" s="3" t="n"/>
-      <c r="K53" s="3" t="n"/>
-      <c r="L53" s="3" t="n"/>
-      <c r="M53" s="3" t="n"/>
-      <c r="N53" s="3" t="n"/>
-      <c r="O53" s="3" t="n"/>
+      <c r="J53" s="3" t="n">
+        <v>0.543</v>
+      </c>
+      <c r="K53" s="3" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="L53" s="3" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M53" s="3" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="N53" s="3" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="O53" s="3" t="n">
+        <v>-0.068</v>
+      </c>
       <c r="P53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="Q53" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -4081,16 +4235,30 @@
       <c r="I54" s="3" t="n">
         <v>0.352</v>
       </c>
-      <c r="J54" s="3" t="n"/>
-      <c r="K54" s="3" t="n"/>
-      <c r="L54" s="3" t="n"/>
-      <c r="M54" s="3" t="n"/>
-      <c r="N54" s="3" t="n"/>
-      <c r="O54" s="3" t="n"/>
+      <c r="J54" s="3" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="K54" s="3" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="L54" s="3" t="n">
+        <v>-0.032</v>
+      </c>
+      <c r="M54" s="3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N54" s="3" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="O54" s="3" t="n">
+        <v>-0.031</v>
+      </c>
       <c r="P54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="Q54" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -4205,16 +4373,30 @@
       <c r="I56" s="3" t="n">
         <v>0.534</v>
       </c>
-      <c r="J56" s="3" t="n"/>
-      <c r="K56" s="3" t="n"/>
-      <c r="L56" s="3" t="n"/>
-      <c r="M56" s="3" t="n"/>
-      <c r="N56" s="3" t="n"/>
-      <c r="O56" s="3" t="n"/>
+      <c r="J56" s="3" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="K56" s="3" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="L56" s="3" t="n">
+        <v>-0.026</v>
+      </c>
+      <c r="M56" s="3" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="N56" s="3" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="O56" s="3" t="n">
+        <v>-0.011</v>
+      </c>
       <c r="P56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q56" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -4260,16 +4442,30 @@
       <c r="I57" s="3" t="n">
         <v>0.387</v>
       </c>
-      <c r="J57" s="3" t="n"/>
-      <c r="K57" s="3" t="n"/>
-      <c r="L57" s="3" t="n"/>
-      <c r="M57" s="3" t="n"/>
-      <c r="N57" s="3" t="n"/>
-      <c r="O57" s="3" t="n"/>
+      <c r="J57" s="3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="K57" s="3" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="L57" s="3" t="n">
+        <v>-0.031</v>
+      </c>
+      <c r="M57" s="3" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="N57" s="3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="O57" s="3" t="n">
+        <v>-0.054</v>
+      </c>
       <c r="P57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q57" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -4384,16 +4580,30 @@
       <c r="I59" s="3" t="n">
         <v>0.485</v>
       </c>
-      <c r="J59" s="3" t="n"/>
-      <c r="K59" s="3" t="n"/>
-      <c r="L59" s="3" t="n"/>
-      <c r="M59" s="3" t="n"/>
-      <c r="N59" s="3" t="n"/>
-      <c r="O59" s="3" t="n"/>
+      <c r="J59" s="3" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="K59" s="3" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="L59" s="3" t="n">
+        <v>-0.017</v>
+      </c>
+      <c r="M59" s="3" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="N59" s="3" t="n">
+        <v>0.756</v>
+      </c>
+      <c r="O59" s="3" t="n">
+        <v>0.016</v>
+      </c>
       <c r="P59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="3" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="Q59" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -4439,16 +4649,30 @@
       <c r="I60" s="3" t="n">
         <v>0.341</v>
       </c>
-      <c r="J60" s="3" t="n"/>
-      <c r="K60" s="3" t="n"/>
-      <c r="L60" s="3" t="n"/>
-      <c r="M60" s="3" t="n"/>
-      <c r="N60" s="3" t="n"/>
-      <c r="O60" s="3" t="n"/>
+      <c r="J60" s="3" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="K60" s="3" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="L60" s="3" t="n">
+        <v>-0.026</v>
+      </c>
+      <c r="M60" s="3" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="N60" s="3" t="n">
+        <v>0.613</v>
+      </c>
+      <c r="O60" s="3" t="n">
+        <v>-0.022</v>
+      </c>
       <c r="P60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q60" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -4563,16 +4787,30 @@
       <c r="I62" s="3" t="n">
         <v>0.604</v>
       </c>
-      <c r="J62" s="3" t="n"/>
-      <c r="K62" s="3" t="n"/>
-      <c r="L62" s="3" t="n"/>
-      <c r="M62" s="3" t="n"/>
-      <c r="N62" s="3" t="n"/>
-      <c r="O62" s="3" t="n"/>
+      <c r="J62" s="3" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="K62" s="3" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="L62" s="3" t="n">
+        <v>-0.041</v>
+      </c>
+      <c r="M62" s="3" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="N62" s="3" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="O62" s="3" t="n">
+        <v>-0.025</v>
+      </c>
       <c r="P62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="Q62" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -4618,16 +4856,30 @@
       <c r="I63" s="3" t="n">
         <v>0.34</v>
       </c>
-      <c r="J63" s="3" t="n"/>
-      <c r="K63" s="3" t="n"/>
-      <c r="L63" s="3" t="n"/>
-      <c r="M63" s="3" t="n"/>
-      <c r="N63" s="3" t="n"/>
-      <c r="O63" s="3" t="n"/>
+      <c r="J63" s="3" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K63" s="3" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="L63" s="3" t="n">
+        <v>-0.008999999999999999</v>
+      </c>
+      <c r="M63" s="3" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="N63" s="3" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="O63" s="3" t="n">
+        <v>0.078</v>
+      </c>
       <c r="P63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="Q63" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -4742,16 +4994,30 @@
       <c r="I65" s="3" t="n">
         <v>0.553</v>
       </c>
-      <c r="J65" s="3" t="n"/>
-      <c r="K65" s="3" t="n"/>
-      <c r="L65" s="3" t="n"/>
-      <c r="M65" s="3" t="n"/>
-      <c r="N65" s="3" t="n"/>
-      <c r="O65" s="3" t="n"/>
+      <c r="J65" s="3" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="K65" s="3" t="n">
+        <v>-0.026</v>
+      </c>
+      <c r="L65" s="3" t="n">
+        <v>-0.051</v>
+      </c>
+      <c r="M65" s="3" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="N65" s="3" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="O65" s="3" t="n">
+        <v>-0.092</v>
+      </c>
       <c r="P65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q65" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4797,16 +5063,30 @@
       <c r="I66" s="3" t="n">
         <v>0.381</v>
       </c>
-      <c r="J66" s="3" t="n"/>
-      <c r="K66" s="3" t="n"/>
-      <c r="L66" s="3" t="n"/>
-      <c r="M66" s="3" t="n"/>
-      <c r="N66" s="3" t="n"/>
-      <c r="O66" s="3" t="n"/>
+      <c r="J66" s="3" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="K66" s="3" t="n">
+        <v>-0.016</v>
+      </c>
+      <c r="L66" s="3" t="n">
+        <v>-0.037</v>
+      </c>
+      <c r="M66" s="3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N66" s="3" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="O66" s="3" t="n">
+        <v>-0.066</v>
+      </c>
       <c r="P66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q66" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4921,16 +5201,30 @@
       <c r="I68" s="3" t="n">
         <v>0.471</v>
       </c>
-      <c r="J68" s="3" t="n"/>
-      <c r="K68" s="3" t="n"/>
-      <c r="L68" s="3" t="n"/>
-      <c r="M68" s="3" t="n"/>
-      <c r="N68" s="3" t="n"/>
-      <c r="O68" s="3" t="n"/>
+      <c r="J68" s="3" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="K68" s="3" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="L68" s="3" t="n">
+        <v>-0.021</v>
+      </c>
+      <c r="M68" s="3" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="N68" s="3" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="O68" s="3" t="n">
+        <v>0.011</v>
+      </c>
       <c r="P68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q68" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q68" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -4976,16 +5270,30 @@
       <c r="I69" s="3" t="n">
         <v>0.32</v>
       </c>
-      <c r="J69" s="3" t="n"/>
-      <c r="K69" s="3" t="n"/>
-      <c r="L69" s="3" t="n"/>
-      <c r="M69" s="3" t="n"/>
-      <c r="N69" s="3" t="n"/>
-      <c r="O69" s="3" t="n"/>
+      <c r="J69" s="3" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="K69" s="3" t="n">
+        <v>-0.014</v>
+      </c>
+      <c r="L69" s="3" t="n">
+        <v>-0.035</v>
+      </c>
+      <c r="M69" s="3" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="N69" s="3" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="O69" s="3" t="n">
+        <v>-0.06</v>
+      </c>
       <c r="P69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q69" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q69" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -5100,16 +5408,30 @@
       <c r="I71" s="3" t="n">
         <v>0.534</v>
       </c>
-      <c r="J71" s="3" t="n"/>
-      <c r="K71" s="3" t="n"/>
-      <c r="L71" s="3" t="n"/>
-      <c r="M71" s="3" t="n"/>
-      <c r="N71" s="3" t="n"/>
-      <c r="O71" s="3" t="n"/>
+      <c r="J71" s="3" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="K71" s="3" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="L71" s="3" t="n">
+        <v>-0.041</v>
+      </c>
+      <c r="M71" s="3" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="N71" s="3" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="O71" s="3" t="n">
+        <v>-0.06900000000000001</v>
+      </c>
       <c r="P71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q71" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q71" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -5155,16 +5477,30 @@
       <c r="I72" s="3" t="n">
         <v>0.333</v>
       </c>
-      <c r="J72" s="3" t="n"/>
-      <c r="K72" s="3" t="n"/>
-      <c r="L72" s="3" t="n"/>
-      <c r="M72" s="3" t="n"/>
-      <c r="N72" s="3" t="n"/>
-      <c r="O72" s="3" t="n"/>
+      <c r="J72" s="3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="K72" s="3" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="L72" s="3" t="n">
+        <v>-0.024</v>
+      </c>
+      <c r="M72" s="3" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="N72" s="3" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="O72" s="3" t="n">
+        <v>-0.013</v>
+      </c>
       <c r="P72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q72" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -5279,16 +5615,30 @@
       <c r="I74" s="3" t="n">
         <v>0.554</v>
       </c>
-      <c r="J74" s="3" t="n"/>
-      <c r="K74" s="3" t="n"/>
-      <c r="L74" s="3" t="n"/>
-      <c r="M74" s="3" t="n"/>
-      <c r="N74" s="3" t="n"/>
-      <c r="O74" s="3" t="n"/>
+      <c r="J74" s="3" t="n">
+        <v>0.547</v>
+      </c>
+      <c r="K74" s="3" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="L74" s="3" t="n">
+        <v>-0.039</v>
+      </c>
+      <c r="M74" s="3" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="N74" s="3" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="O74" s="3" t="n">
+        <v>-0.027</v>
+      </c>
       <c r="P74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q74" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="Q74" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -5334,16 +5684,30 @@
       <c r="I75" s="3" t="n">
         <v>0.317</v>
       </c>
-      <c r="J75" s="3" t="n"/>
-      <c r="K75" s="3" t="n"/>
-      <c r="L75" s="3" t="n"/>
-      <c r="M75" s="3" t="n"/>
-      <c r="N75" s="3" t="n"/>
-      <c r="O75" s="3" t="n"/>
+      <c r="J75" s="3" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="K75" s="3" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="L75" s="3" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="M75" s="3" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="N75" s="3" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="O75" s="3" t="n">
+        <v>-0.013</v>
+      </c>
       <c r="P75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q75" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="Q75" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -5458,16 +5822,30 @@
       <c r="I77" s="3" t="n">
         <v>0.547</v>
       </c>
-      <c r="J77" s="3" t="n"/>
-      <c r="K77" s="3" t="n"/>
-      <c r="L77" s="3" t="n"/>
-      <c r="M77" s="3" t="n"/>
-      <c r="N77" s="3" t="n"/>
-      <c r="O77" s="3" t="n"/>
+      <c r="J77" s="3" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="K77" s="3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="L77" s="3" t="n">
+        <v>-0.045</v>
+      </c>
+      <c r="M77" s="3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N77" s="3" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="O77" s="3" t="n">
+        <v>-0.07099999999999999</v>
+      </c>
       <c r="P77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q77" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q77" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -5513,16 +5891,30 @@
       <c r="I78" s="3" t="n">
         <v>0.365</v>
       </c>
-      <c r="J78" s="3" t="n"/>
-      <c r="K78" s="3" t="n"/>
-      <c r="L78" s="3" t="n"/>
-      <c r="M78" s="3" t="n"/>
-      <c r="N78" s="3" t="n"/>
-      <c r="O78" s="3" t="n"/>
+      <c r="J78" s="3" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="K78" s="3" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="L78" s="3" t="n">
+        <v>-0.014</v>
+      </c>
+      <c r="M78" s="3" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="N78" s="3" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="O78" s="3" t="n">
+        <v>0.026</v>
+      </c>
       <c r="P78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q78" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -5637,16 +6029,30 @@
       <c r="I80" s="3" t="n">
         <v>0.533</v>
       </c>
-      <c r="J80" s="3" t="n"/>
-      <c r="K80" s="3" t="n"/>
-      <c r="L80" s="3" t="n"/>
-      <c r="M80" s="3" t="n"/>
-      <c r="N80" s="3" t="n"/>
-      <c r="O80" s="3" t="n"/>
+      <c r="J80" s="3" t="n">
+        <v>0.496</v>
+      </c>
+      <c r="K80" s="3" t="n">
+        <v>-0.037</v>
+      </c>
+      <c r="L80" s="3" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="M80" s="3" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>-0.129</v>
+      </c>
       <c r="P80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q80" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q80" s="3" t="n">
+        <v>0.252</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -5692,16 +6098,30 @@
       <c r="I81" s="3" t="n">
         <v>0.335</v>
       </c>
-      <c r="J81" s="3" t="n"/>
-      <c r="K81" s="3" t="n"/>
-      <c r="L81" s="3" t="n"/>
-      <c r="M81" s="3" t="n"/>
-      <c r="N81" s="3" t="n"/>
-      <c r="O81" s="3" t="n"/>
+      <c r="J81" s="3" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="K81" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="L81" s="3" t="n">
+        <v>-0.029</v>
+      </c>
+      <c r="M81" s="3" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="N81" s="3" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="O81" s="3" t="n">
+        <v>-0.046</v>
+      </c>
       <c r="P81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q81" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q81" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -6666,7 +7086,7 @@
         <v>499</v>
       </c>
       <c r="Q95" s="3" t="n">
-        <v>0.018</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="96">
@@ -6735,7 +7155,7 @@
         <v>500</v>
       </c>
       <c r="Q96" s="3" t="n">
-        <v>0.018</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="97">
@@ -7356,7 +7776,7 @@
         <v>500</v>
       </c>
       <c r="Q105" s="3" t="n">
-        <v>0.703</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -7494,7 +7914,7 @@
         <v>500</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>0.018</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="108">
@@ -7563,7 +7983,7 @@
         <v>500</v>
       </c>
       <c r="Q108" s="3" t="n">
-        <v>0.018</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="109">
@@ -7908,7 +8328,7 @@
         <v>500</v>
       </c>
       <c r="Q113" s="3" t="n">
-        <v>0.299</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="114">
@@ -8115,7 +8535,7 @@
         <v>500</v>
       </c>
       <c r="Q116" s="3" t="n">
-        <v>0.312</v>
+        <v>0.737</v>
       </c>
     </row>
     <row r="117">
@@ -8184,7 +8604,7 @@
         <v>500</v>
       </c>
       <c r="Q117" s="3" t="n">
-        <v>0.018</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="118">
@@ -8300,16 +8720,30 @@
       <c r="I119" s="3" t="n">
         <v>0.547</v>
       </c>
-      <c r="J119" s="3" t="n"/>
-      <c r="K119" s="3" t="n"/>
-      <c r="L119" s="3" t="n"/>
-      <c r="M119" s="3" t="n"/>
-      <c r="N119" s="3" t="n"/>
-      <c r="O119" s="3" t="n"/>
+      <c r="J119" s="3" t="n">
+        <v>0.549</v>
+      </c>
+      <c r="K119" s="3" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="L119" s="3" t="n">
+        <v>-0.023</v>
+      </c>
+      <c r="M119" s="3" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="N119" s="3" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="O119" s="3" t="n">
+        <v>0.007</v>
+      </c>
       <c r="P119" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q119" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q119" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -8355,16 +8789,30 @@
       <c r="I120" s="3" t="n">
         <v>0.349</v>
       </c>
-      <c r="J120" s="3" t="n"/>
-      <c r="K120" s="3" t="n"/>
-      <c r="L120" s="3" t="n"/>
-      <c r="M120" s="3" t="n"/>
-      <c r="N120" s="3" t="n"/>
-      <c r="O120" s="3" t="n"/>
+      <c r="J120" s="3" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="K120" s="3" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="L120" s="3" t="n">
+        <v>-0.017</v>
+      </c>
+      <c r="M120" s="3" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="N120" s="3" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="O120" s="3" t="n">
+        <v>0.023</v>
+      </c>
       <c r="P120" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q120" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q120" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -8479,16 +8927,30 @@
       <c r="I122" s="3" t="n">
         <v>0.584</v>
       </c>
-      <c r="J122" s="3" t="n"/>
-      <c r="K122" s="3" t="n"/>
-      <c r="L122" s="3" t="n"/>
-      <c r="M122" s="3" t="n"/>
-      <c r="N122" s="3" t="n"/>
-      <c r="O122" s="3" t="n"/>
+      <c r="J122" s="3" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="K122" s="3" t="n">
+        <v>-0.029</v>
+      </c>
+      <c r="L122" s="3" t="n">
+        <v>-0.063</v>
+      </c>
+      <c r="M122" s="3" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="N122" s="3" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="O122" s="3" t="n">
+        <v>-0.099</v>
+      </c>
       <c r="P122" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q122" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="Q122" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -8534,16 +8996,30 @@
       <c r="I123" s="3" t="n">
         <v>0.35</v>
       </c>
-      <c r="J123" s="3" t="n"/>
-      <c r="K123" s="3" t="n"/>
-      <c r="L123" s="3" t="n"/>
-      <c r="M123" s="3" t="n"/>
-      <c r="N123" s="3" t="n"/>
-      <c r="O123" s="3" t="n"/>
+      <c r="J123" s="3" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="K123" s="3" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="L123" s="3" t="n">
+        <v>-0.043</v>
+      </c>
+      <c r="M123" s="3" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="N123" s="3" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="O123" s="3" t="n">
+        <v>-0.052</v>
+      </c>
       <c r="P123" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q123" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="Q123" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -8658,16 +9134,30 @@
       <c r="I125" s="3" t="n">
         <v>0.543</v>
       </c>
-      <c r="J125" s="3" t="n"/>
-      <c r="K125" s="3" t="n"/>
-      <c r="L125" s="3" t="n"/>
-      <c r="M125" s="3" t="n"/>
-      <c r="N125" s="3" t="n"/>
-      <c r="O125" s="3" t="n"/>
+      <c r="J125" s="3" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="K125" s="3" t="n">
+        <v>-0.019</v>
+      </c>
+      <c r="L125" s="3" t="n">
+        <v>-0.043</v>
+      </c>
+      <c r="M125" s="3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N125" s="3" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="O125" s="3" t="n">
+        <v>-0.073</v>
+      </c>
       <c r="P125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q125" s="3" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="Q125" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -8713,16 +9203,30 @@
       <c r="I126" s="3" t="n">
         <v>0.38</v>
       </c>
-      <c r="J126" s="3" t="n"/>
-      <c r="K126" s="3" t="n"/>
-      <c r="L126" s="3" t="n"/>
-      <c r="M126" s="3" t="n"/>
-      <c r="N126" s="3" t="n"/>
-      <c r="O126" s="3" t="n"/>
+      <c r="J126" s="3" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="K126" s="3" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="L126" s="3" t="n">
+        <v>-0.032</v>
+      </c>
+      <c r="M126" s="3" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="N126" s="3" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="O126" s="3" t="n">
+        <v>-0.059</v>
+      </c>
       <c r="P126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q126" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q126" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -8837,16 +9341,30 @@
       <c r="I128" s="3" t="n">
         <v>0.518</v>
       </c>
-      <c r="J128" s="3" t="n"/>
-      <c r="K128" s="3" t="n"/>
-      <c r="L128" s="3" t="n"/>
-      <c r="M128" s="3" t="n"/>
-      <c r="N128" s="3" t="n"/>
-      <c r="O128" s="3" t="n"/>
+      <c r="J128" s="3" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="K128" s="3" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="L128" s="3" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="M128" s="3" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="N128" s="3" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="O128" s="3" t="n">
+        <v>-0.022</v>
+      </c>
       <c r="P128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q128" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q128" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -8892,16 +9410,30 @@
       <c r="I129" s="3" t="n">
         <v>0.357</v>
       </c>
-      <c r="J129" s="3" t="n"/>
-      <c r="K129" s="3" t="n"/>
-      <c r="L129" s="3" t="n"/>
-      <c r="M129" s="3" t="n"/>
-      <c r="N129" s="3" t="n"/>
-      <c r="O129" s="3" t="n"/>
+      <c r="J129" s="3" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="K129" s="3" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="L129" s="3" t="n">
+        <v>-0.043</v>
+      </c>
+      <c r="M129" s="3" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="N129" s="3" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="O129" s="3" t="n">
+        <v>-0.12</v>
+      </c>
       <c r="P129" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q129" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q129" s="3" t="n">
+        <v>0.472</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -9016,16 +9548,30 @@
       <c r="I131" s="3" t="n">
         <v>0.572</v>
       </c>
-      <c r="J131" s="3" t="n"/>
-      <c r="K131" s="3" t="n"/>
-      <c r="L131" s="3" t="n"/>
-      <c r="M131" s="3" t="n"/>
-      <c r="N131" s="3" t="n"/>
-      <c r="O131" s="3" t="n"/>
+      <c r="J131" s="3" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="K131" s="3" t="n">
+        <v>-0.014</v>
+      </c>
+      <c r="L131" s="3" t="n">
+        <v>-0.048</v>
+      </c>
+      <c r="M131" s="3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N131" s="3" t="n">
+        <v>0.439</v>
+      </c>
+      <c r="O131" s="3" t="n">
+        <v>-0.048</v>
+      </c>
       <c r="P131" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q131" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="Q131" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -9071,16 +9617,30 @@
       <c r="I132" s="3" t="n">
         <v>0.36</v>
       </c>
-      <c r="J132" s="3" t="n"/>
-      <c r="K132" s="3" t="n"/>
-      <c r="L132" s="3" t="n"/>
-      <c r="M132" s="3" t="n"/>
-      <c r="N132" s="3" t="n"/>
-      <c r="O132" s="3" t="n"/>
+      <c r="J132" s="3" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="K132" s="3" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="L132" s="3" t="n">
+        <v>-0.042</v>
+      </c>
+      <c r="M132" s="3" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="N132" s="3" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="O132" s="3" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="P132" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q132" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="Q132" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -9195,16 +9755,30 @@
       <c r="I134" s="3" t="n">
         <v>0.531</v>
       </c>
-      <c r="J134" s="3" t="n"/>
-      <c r="K134" s="3" t="n"/>
-      <c r="L134" s="3" t="n"/>
-      <c r="M134" s="3" t="n"/>
-      <c r="N134" s="3" t="n"/>
-      <c r="O134" s="3" t="n"/>
+      <c r="J134" s="3" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="K134" s="3" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="L134" s="3" t="n">
+        <v>-0.036</v>
+      </c>
+      <c r="M134" s="3" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="N134" s="3" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="O134" s="3" t="n">
+        <v>-0.043</v>
+      </c>
       <c r="P134" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q134" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q134" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -9250,16 +9824,30 @@
       <c r="I135" s="3" t="n">
         <v>0.376</v>
       </c>
-      <c r="J135" s="3" t="n"/>
-      <c r="K135" s="3" t="n"/>
-      <c r="L135" s="3" t="n"/>
-      <c r="M135" s="3" t="n"/>
-      <c r="N135" s="3" t="n"/>
-      <c r="O135" s="3" t="n"/>
+      <c r="J135" s="3" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="K135" s="3" t="n">
+        <v>-0.019</v>
+      </c>
+      <c r="L135" s="3" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="M135" s="3" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="N135" s="3" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="O135" s="3" t="n">
+        <v>-0.077</v>
+      </c>
       <c r="P135" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q135" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q135" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -9374,16 +9962,30 @@
       <c r="I137" s="3" t="n">
         <v>0.495</v>
       </c>
-      <c r="J137" s="3" t="n"/>
-      <c r="K137" s="3" t="n"/>
-      <c r="L137" s="3" t="n"/>
-      <c r="M137" s="3" t="n"/>
-      <c r="N137" s="3" t="n"/>
-      <c r="O137" s="3" t="n"/>
+      <c r="J137" s="3" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K137" s="3" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="L137" s="3" t="n">
+        <v>-0.041</v>
+      </c>
+      <c r="M137" s="3" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="N137" s="3" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="O137" s="3" t="n">
+        <v>-0.051</v>
+      </c>
       <c r="P137" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q137" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q137" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -9429,16 +10031,30 @@
       <c r="I138" s="3" t="n">
         <v>0.332</v>
       </c>
-      <c r="J138" s="3" t="n"/>
-      <c r="K138" s="3" t="n"/>
-      <c r="L138" s="3" t="n"/>
-      <c r="M138" s="3" t="n"/>
-      <c r="N138" s="3" t="n"/>
-      <c r="O138" s="3" t="n"/>
+      <c r="J138" s="3" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="K138" s="3" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="L138" s="3" t="n">
+        <v>-0.037</v>
+      </c>
+      <c r="M138" s="3" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="N138" s="3" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="O138" s="3" t="n">
+        <v>-0.076</v>
+      </c>
       <c r="P138" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q138" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q138" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -9553,16 +10169,30 @@
       <c r="I140" s="3" t="n">
         <v>0.5639999999999999</v>
       </c>
-      <c r="J140" s="3" t="n"/>
-      <c r="K140" s="3" t="n"/>
-      <c r="L140" s="3" t="n"/>
-      <c r="M140" s="3" t="n"/>
-      <c r="N140" s="3" t="n"/>
-      <c r="O140" s="3" t="n"/>
+      <c r="J140" s="3" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="K140" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L140" s="3" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="M140" s="3" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="N140" s="3" t="n">
+        <v>0.457</v>
+      </c>
+      <c r="O140" s="3" t="n">
+        <v>0.035</v>
+      </c>
       <c r="P140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q140" s="3" t="n"/>
+        <v>498</v>
+      </c>
+      <c r="Q140" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -9608,16 +10238,30 @@
       <c r="I141" s="3" t="n">
         <v>0.406</v>
       </c>
-      <c r="J141" s="3" t="n"/>
-      <c r="K141" s="3" t="n"/>
-      <c r="L141" s="3" t="n"/>
-      <c r="M141" s="3" t="n"/>
-      <c r="N141" s="3" t="n"/>
-      <c r="O141" s="3" t="n"/>
+      <c r="J141" s="3" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="K141" s="3" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="L141" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="M141" s="3" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="N141" s="3" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="O141" s="3" t="n">
+        <v>0.047</v>
+      </c>
       <c r="P141" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q141" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q141" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -9732,16 +10376,30 @@
       <c r="I143" s="3" t="n">
         <v>0.572</v>
       </c>
-      <c r="J143" s="3" t="n"/>
-      <c r="K143" s="3" t="n"/>
-      <c r="L143" s="3" t="n"/>
-      <c r="M143" s="3" t="n"/>
-      <c r="N143" s="3" t="n"/>
-      <c r="O143" s="3" t="n"/>
+      <c r="J143" s="3" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="K143" s="3" t="n">
+        <v>-0.014</v>
+      </c>
+      <c r="L143" s="3" t="n">
+        <v>-0.048</v>
+      </c>
+      <c r="M143" s="3" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="N143" s="3" t="n">
+        <v>0.439</v>
+      </c>
+      <c r="O143" s="3" t="n">
+        <v>-0.05</v>
+      </c>
       <c r="P143" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q143" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="Q143" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -9787,16 +10445,30 @@
       <c r="I144" s="3" t="n">
         <v>0.372</v>
       </c>
-      <c r="J144" s="3" t="n"/>
-      <c r="K144" s="3" t="n"/>
-      <c r="L144" s="3" t="n"/>
-      <c r="M144" s="3" t="n"/>
-      <c r="N144" s="3" t="n"/>
-      <c r="O144" s="3" t="n"/>
+      <c r="J144" s="3" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="K144" s="3" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="L144" s="3" t="n">
+        <v>-0.031</v>
+      </c>
+      <c r="M144" s="3" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="N144" s="3" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="O144" s="3" t="n">
+        <v>-0.011</v>
+      </c>
       <c r="P144" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q144" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="Q144" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -9911,16 +10583,30 @@
       <c r="I146" s="3" t="n">
         <v>0.539</v>
       </c>
-      <c r="J146" s="3" t="n"/>
-      <c r="K146" s="3" t="n"/>
-      <c r="L146" s="3" t="n"/>
-      <c r="M146" s="3" t="n"/>
-      <c r="N146" s="3" t="n"/>
-      <c r="O146" s="3" t="n"/>
+      <c r="J146" s="3" t="n">
+        <v>0.537</v>
+      </c>
+      <c r="K146" s="3" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="L146" s="3" t="n">
+        <v>-0.027</v>
+      </c>
+      <c r="M146" s="3" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="N146" s="3" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="O146" s="3" t="n">
+        <v>-0.007</v>
+      </c>
       <c r="P146" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q146" s="3" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="Q146" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -9966,16 +10652,30 @@
       <c r="I147" s="3" t="n">
         <v>0.374</v>
       </c>
-      <c r="J147" s="3" t="n"/>
-      <c r="K147" s="3" t="n"/>
-      <c r="L147" s="3" t="n"/>
-      <c r="M147" s="3" t="n"/>
-      <c r="N147" s="3" t="n"/>
-      <c r="O147" s="3" t="n"/>
+      <c r="J147" s="3" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="K147" s="3" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="L147" s="3" t="n">
+        <v>-0.027</v>
+      </c>
+      <c r="M147" s="3" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="N147" s="3" t="n">
+        <v>0.464</v>
+      </c>
+      <c r="O147" s="3" t="n">
+        <v>-0.031</v>
+      </c>
       <c r="P147" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q147" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q147" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -10090,16 +10790,30 @@
       <c r="I149" s="3" t="n">
         <v>0.502</v>
       </c>
-      <c r="J149" s="3" t="n"/>
-      <c r="K149" s="3" t="n"/>
-      <c r="L149" s="3" t="n"/>
-      <c r="M149" s="3" t="n"/>
-      <c r="N149" s="3" t="n"/>
-      <c r="O149" s="3" t="n"/>
+      <c r="J149" s="3" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="K149" s="3" t="n">
+        <v>-0.031</v>
+      </c>
+      <c r="L149" s="3" t="n">
+        <v>-0.055</v>
+      </c>
+      <c r="M149" s="3" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="N149" s="3" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="O149" s="3" t="n">
+        <v>-0.111</v>
+      </c>
       <c r="P149" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q149" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q149" s="3" t="n">
+        <v>0.754</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -10145,16 +10859,30 @@
       <c r="I150" s="3" t="n">
         <v>0.34</v>
       </c>
-      <c r="J150" s="3" t="n"/>
-      <c r="K150" s="3" t="n"/>
-      <c r="L150" s="3" t="n"/>
-      <c r="M150" s="3" t="n"/>
-      <c r="N150" s="3" t="n"/>
-      <c r="O150" s="3" t="n"/>
+      <c r="J150" s="3" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="K150" s="3" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="L150" s="3" t="n">
+        <v>-0.043</v>
+      </c>
+      <c r="M150" s="3" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="N150" s="3" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="O150" s="3" t="n">
+        <v>-0.12</v>
+      </c>
       <c r="P150" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q150" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q150" s="3" t="n">
+        <v>0.493</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -10269,16 +10997,30 @@
       <c r="I152" s="3" t="n">
         <v>0.735</v>
       </c>
-      <c r="J152" s="3" t="n"/>
-      <c r="K152" s="3" t="n"/>
-      <c r="L152" s="3" t="n"/>
-      <c r="M152" s="3" t="n"/>
-      <c r="N152" s="3" t="n"/>
-      <c r="O152" s="3" t="n"/>
+      <c r="J152" s="3" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="K152" s="3" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="L152" s="3" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="M152" s="3" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="N152" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O152" s="3" t="n">
+        <v>0.234</v>
+      </c>
       <c r="P152" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q152" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q152" s="3" t="n">
+        <v>0.036</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -10324,16 +11066,30 @@
       <c r="I153" s="3" t="n">
         <v>0.583</v>
       </c>
-      <c r="J153" s="3" t="n"/>
-      <c r="K153" s="3" t="n"/>
-      <c r="L153" s="3" t="n"/>
-      <c r="M153" s="3" t="n"/>
-      <c r="N153" s="3" t="n"/>
-      <c r="O153" s="3" t="n"/>
+      <c r="J153" s="3" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="K153" s="3" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="L153" s="3" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="M153" s="3" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="N153" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" s="3" t="n">
+        <v>0.275</v>
+      </c>
       <c r="P153" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q153" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q153" s="3" t="n">
+        <v>0.036</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -10448,16 +11204,30 @@
       <c r="I155" s="3" t="n">
         <v>0.62</v>
       </c>
-      <c r="J155" s="3" t="n"/>
-      <c r="K155" s="3" t="n"/>
-      <c r="L155" s="3" t="n"/>
-      <c r="M155" s="3" t="n"/>
-      <c r="N155" s="3" t="n"/>
-      <c r="O155" s="3" t="n"/>
+      <c r="J155" s="3" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="K155" s="3" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="L155" s="3" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="M155" s="3" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="N155" s="3" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="O155" s="3" t="n">
+        <v>0.154</v>
+      </c>
       <c r="P155" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q155" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="Q155" s="3" t="n">
+        <v>0.579</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -10503,16 +11273,30 @@
       <c r="I156" s="3" t="n">
         <v>0.419</v>
       </c>
-      <c r="J156" s="3" t="n"/>
-      <c r="K156" s="3" t="n"/>
-      <c r="L156" s="3" t="n"/>
-      <c r="M156" s="3" t="n"/>
-      <c r="N156" s="3" t="n"/>
-      <c r="O156" s="3" t="n"/>
+      <c r="J156" s="3" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="K156" s="3" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="L156" s="3" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="M156" s="3" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="N156" s="3" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="O156" s="3" t="n">
+        <v>0.08699999999999999</v>
+      </c>
       <c r="P156" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q156" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="Q156" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -10627,16 +11411,30 @@
       <c r="I158" s="3" t="n">
         <v>0.528</v>
       </c>
-      <c r="J158" s="3" t="n"/>
-      <c r="K158" s="3" t="n"/>
-      <c r="L158" s="3" t="n"/>
-      <c r="M158" s="3" t="n"/>
-      <c r="N158" s="3" t="n"/>
-      <c r="O158" s="3" t="n"/>
+      <c r="J158" s="3" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="K158" s="3" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="L158" s="3" t="n">
+        <v>-0.028</v>
+      </c>
+      <c r="M158" s="3" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="N158" s="3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="O158" s="3" t="n">
+        <v>-0.006</v>
+      </c>
       <c r="P158" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q158" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q158" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -10682,16 +11480,30 @@
       <c r="I159" s="3" t="n">
         <v>0.373</v>
       </c>
-      <c r="J159" s="3" t="n"/>
-      <c r="K159" s="3" t="n"/>
-      <c r="L159" s="3" t="n"/>
-      <c r="M159" s="3" t="n"/>
-      <c r="N159" s="3" t="n"/>
-      <c r="O159" s="3" t="n"/>
+      <c r="J159" s="3" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="K159" s="3" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="L159" s="3" t="n">
+        <v>-0.034</v>
+      </c>
+      <c r="M159" s="3" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="N159" s="3" t="n">
+        <v>0.514</v>
+      </c>
+      <c r="O159" s="3" t="n">
+        <v>-0.029</v>
+      </c>
       <c r="P159" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q159" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q159" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -10806,16 +11618,30 @@
       <c r="I161" s="3" t="n">
         <v>0.469</v>
       </c>
-      <c r="J161" s="3" t="n"/>
-      <c r="K161" s="3" t="n"/>
-      <c r="L161" s="3" t="n"/>
-      <c r="M161" s="3" t="n"/>
-      <c r="N161" s="3" t="n"/>
-      <c r="O161" s="3" t="n"/>
+      <c r="J161" s="3" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="K161" s="3" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="L161" s="3" t="n">
+        <v>-0.023</v>
+      </c>
+      <c r="M161" s="3" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="N161" s="3" t="n">
+        <v>0.911</v>
+      </c>
+      <c r="O161" s="3" t="n">
+        <v>0.007</v>
+      </c>
       <c r="P161" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q161" s="3" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="Q161" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -10861,16 +11687,30 @@
       <c r="I162" s="3" t="n">
         <v>0.323</v>
       </c>
-      <c r="J162" s="3" t="n"/>
-      <c r="K162" s="3" t="n"/>
-      <c r="L162" s="3" t="n"/>
-      <c r="M162" s="3" t="n"/>
-      <c r="N162" s="3" t="n"/>
-      <c r="O162" s="3" t="n"/>
+      <c r="J162" s="3" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="K162" s="3" t="n">
+        <v>-0.016</v>
+      </c>
+      <c r="L162" s="3" t="n">
+        <v>-0.039</v>
+      </c>
+      <c r="M162" s="3" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="N162" s="3" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="O162" s="3" t="n">
+        <v>-0.06</v>
+      </c>
       <c r="P162" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q162" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q162" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -11007,7 +11847,7 @@
         <v>500</v>
       </c>
       <c r="Q164" s="3" t="n">
-        <v>0.9350000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
@@ -11076,7 +11916,7 @@
         <v>500</v>
       </c>
       <c r="Q165" s="3" t="n">
-        <v>0.299</v>
+        <v>0.728</v>
       </c>
     </row>
     <row r="166">
@@ -11490,7 +12330,7 @@
         <v>500</v>
       </c>
       <c r="Q171" s="3" t="n">
-        <v>0.104</v>
+        <v>0.248</v>
       </c>
     </row>
     <row r="172">
@@ -11835,7 +12675,7 @@
         <v>500</v>
       </c>
       <c r="Q176" s="3" t="n">
-        <v>0.018</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="177">
@@ -11904,7 +12744,7 @@
         <v>500</v>
       </c>
       <c r="Q177" s="3" t="n">
-        <v>0.018</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="178">
@@ -12042,7 +12882,7 @@
         <v>279</v>
       </c>
       <c r="Q179" s="3" t="n">
-        <v>0.432</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180">
@@ -12111,7 +12951,7 @@
         <v>279</v>
       </c>
       <c r="Q180" s="3" t="n">
-        <v>0.15</v>
+        <v>0.366</v>
       </c>
     </row>
     <row r="181">
@@ -12663,7 +13503,7 @@
         <v>500</v>
       </c>
       <c r="Q188" s="3" t="n">
-        <v>0.018</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="189">
@@ -12732,7 +13572,7 @@
         <v>500</v>
       </c>
       <c r="Q189" s="3" t="n">
-        <v>0.018</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="190">
@@ -12870,7 +13710,7 @@
         <v>279</v>
       </c>
       <c r="Q191" s="3" t="n">
-        <v>0.018</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="192">
@@ -12939,7 +13779,7 @@
         <v>279</v>
       </c>
       <c r="Q192" s="3" t="n">
-        <v>0.029</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="193">
@@ -13146,7 +13986,7 @@
         <v>500</v>
       </c>
       <c r="Q195" s="3" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196">
@@ -13469,16 +14309,30 @@
       <c r="I200" s="3" t="n">
         <v>0.571</v>
       </c>
-      <c r="J200" s="3" t="n"/>
-      <c r="K200" s="3" t="n"/>
-      <c r="L200" s="3" t="n"/>
-      <c r="M200" s="3" t="n"/>
-      <c r="N200" s="3" t="n"/>
-      <c r="O200" s="3" t="n"/>
+      <c r="J200" s="3" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="K200" s="3" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="L200" s="3" t="n">
+        <v>-0.034</v>
+      </c>
+      <c r="M200" s="3" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="N200" s="3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="O200" s="3" t="n">
+        <v>-0.024</v>
+      </c>
       <c r="P200" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q200" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q200" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -13524,16 +14378,30 @@
       <c r="I201" s="3" t="n">
         <v>0.378</v>
       </c>
-      <c r="J201" s="3" t="n"/>
-      <c r="K201" s="3" t="n"/>
-      <c r="L201" s="3" t="n"/>
-      <c r="M201" s="3" t="n"/>
-      <c r="N201" s="3" t="n"/>
-      <c r="O201" s="3" t="n"/>
+      <c r="J201" s="3" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="K201" s="3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="L201" s="3" t="n">
+        <v>-0.017</v>
+      </c>
+      <c r="M201" s="3" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="N201" s="3" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="O201" s="3" t="n">
+        <v>0.019</v>
+      </c>
       <c r="P201" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q201" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q201" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -13648,16 +14516,30 @@
       <c r="I203" s="3" t="n">
         <v>0.595</v>
       </c>
-      <c r="J203" s="3" t="n"/>
-      <c r="K203" s="3" t="n"/>
-      <c r="L203" s="3" t="n"/>
-      <c r="M203" s="3" t="n"/>
-      <c r="N203" s="3" t="n"/>
-      <c r="O203" s="3" t="n"/>
+      <c r="J203" s="3" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="K203" s="3" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="L203" s="3" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="M203" s="3" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="N203" s="3" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="O203" s="3" t="n">
+        <v>-0.019</v>
+      </c>
       <c r="P203" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q203" s="3" t="n"/>
+        <v>278</v>
+      </c>
+      <c r="Q203" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -13703,16 +14585,30 @@
       <c r="I204" s="3" t="n">
         <v>0.358</v>
       </c>
-      <c r="J204" s="3" t="n"/>
-      <c r="K204" s="3" t="n"/>
-      <c r="L204" s="3" t="n"/>
-      <c r="M204" s="3" t="n"/>
-      <c r="N204" s="3" t="n"/>
-      <c r="O204" s="3" t="n"/>
+      <c r="J204" s="3" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="K204" s="3" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="L204" s="3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="M204" s="3" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="N204" s="3" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="O204" s="3" t="n">
+        <v>0.031</v>
+      </c>
       <c r="P204" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q204" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="Q204" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -13827,16 +14723,30 @@
       <c r="I206" s="3" t="n">
         <v>0.52</v>
       </c>
-      <c r="J206" s="3" t="n"/>
-      <c r="K206" s="3" t="n"/>
-      <c r="L206" s="3" t="n"/>
-      <c r="M206" s="3" t="n"/>
-      <c r="N206" s="3" t="n"/>
-      <c r="O206" s="3" t="n"/>
+      <c r="J206" s="3" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="K206" s="3" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="L206" s="3" t="n">
+        <v>-0.016</v>
+      </c>
+      <c r="M206" s="3" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="N206" s="3" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="O206" s="3" t="n">
+        <v>0.03</v>
+      </c>
       <c r="P206" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q206" s="3" t="n"/>
+        <v>498</v>
+      </c>
+      <c r="Q206" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -13882,16 +14792,30 @@
       <c r="I207" s="3" t="n">
         <v>0.375</v>
       </c>
-      <c r="J207" s="3" t="n"/>
-      <c r="K207" s="3" t="n"/>
-      <c r="L207" s="3" t="n"/>
-      <c r="M207" s="3" t="n"/>
-      <c r="N207" s="3" t="n"/>
-      <c r="O207" s="3" t="n"/>
+      <c r="J207" s="3" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="K207" s="3" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="L207" s="3" t="n">
+        <v>-0.051</v>
+      </c>
+      <c r="M207" s="3" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="N207" s="3" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="O207" s="3" t="n">
+        <v>-0.119</v>
+      </c>
       <c r="P207" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q207" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q207" s="3" t="n">
+        <v>0.42</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -14006,16 +14930,30 @@
       <c r="I209" s="3" t="n">
         <v>0.485</v>
       </c>
-      <c r="J209" s="3" t="n"/>
-      <c r="K209" s="3" t="n"/>
-      <c r="L209" s="3" t="n"/>
-      <c r="M209" s="3" t="n"/>
-      <c r="N209" s="3" t="n"/>
-      <c r="O209" s="3" t="n"/>
+      <c r="J209" s="3" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="K209" s="3" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="L209" s="3" t="n">
+        <v>-0.036</v>
+      </c>
+      <c r="M209" s="3" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="N209" s="3" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="O209" s="3" t="n">
+        <v>-0.041</v>
+      </c>
       <c r="P209" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q209" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q209" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -14061,16 +14999,30 @@
       <c r="I210" s="3" t="n">
         <v>0.333</v>
       </c>
-      <c r="J210" s="3" t="n"/>
-      <c r="K210" s="3" t="n"/>
-      <c r="L210" s="3" t="n"/>
-      <c r="M210" s="3" t="n"/>
-      <c r="N210" s="3" t="n"/>
-      <c r="O210" s="3" t="n"/>
+      <c r="J210" s="3" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="K210" s="3" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="L210" s="3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="M210" s="3" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="N210" s="3" t="n">
+        <v>0.861</v>
+      </c>
+      <c r="O210" s="3" t="n">
+        <v>0.008999999999999999</v>
+      </c>
       <c r="P210" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q210" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q210" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -14185,16 +15137,30 @@
       <c r="I212" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="J212" s="3" t="n"/>
-      <c r="K212" s="3" t="n"/>
-      <c r="L212" s="3" t="n"/>
-      <c r="M212" s="3" t="n"/>
-      <c r="N212" s="3" t="n"/>
-      <c r="O212" s="3" t="n"/>
+      <c r="J212" s="3" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="K212" s="3" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="L212" s="3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="M212" s="3" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="N212" s="3" t="n">
+        <v>0.461</v>
+      </c>
+      <c r="O212" s="3" t="n">
+        <v>0.05</v>
+      </c>
       <c r="P212" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q212" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="Q212" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -14240,16 +15206,30 @@
       <c r="I213" s="3" t="n">
         <v>0.38</v>
       </c>
-      <c r="J213" s="3" t="n"/>
-      <c r="K213" s="3" t="n"/>
-      <c r="L213" s="3" t="n"/>
-      <c r="M213" s="3" t="n"/>
-      <c r="N213" s="3" t="n"/>
-      <c r="O213" s="3" t="n"/>
+      <c r="J213" s="3" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="K213" s="3" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="L213" s="3" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="M213" s="3" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="N213" s="3" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="O213" s="3" t="n">
+        <v>0.082</v>
+      </c>
       <c r="P213" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q213" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="Q213" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -14364,16 +15344,30 @@
       <c r="I215" s="3" t="n">
         <v>0.521</v>
       </c>
-      <c r="J215" s="3" t="n"/>
-      <c r="K215" s="3" t="n"/>
-      <c r="L215" s="3" t="n"/>
-      <c r="M215" s="3" t="n"/>
-      <c r="N215" s="3" t="n"/>
-      <c r="O215" s="3" t="n"/>
+      <c r="J215" s="3" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="K215" s="3" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="L215" s="3" t="n">
+        <v>-0.028</v>
+      </c>
+      <c r="M215" s="3" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="N215" s="3" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="O215" s="3" t="n">
+        <v>-0.015</v>
+      </c>
       <c r="P215" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q215" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q215" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -14419,16 +15413,30 @@
       <c r="I216" s="3" t="n">
         <v>0.358</v>
       </c>
-      <c r="J216" s="3" t="n"/>
-      <c r="K216" s="3" t="n"/>
-      <c r="L216" s="3" t="n"/>
-      <c r="M216" s="3" t="n"/>
-      <c r="N216" s="3" t="n"/>
-      <c r="O216" s="3" t="n"/>
+      <c r="J216" s="3" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="K216" s="3" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="L216" s="3" t="n">
+        <v>-0.023</v>
+      </c>
+      <c r="M216" s="3" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="N216" s="3" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="O216" s="3" t="n">
+        <v>0.008999999999999999</v>
+      </c>
       <c r="P216" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q216" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q216" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -14543,16 +15551,30 @@
       <c r="I218" s="3" t="n">
         <v>0.474</v>
       </c>
-      <c r="J218" s="3" t="n"/>
-      <c r="K218" s="3" t="n"/>
-      <c r="L218" s="3" t="n"/>
-      <c r="M218" s="3" t="n"/>
-      <c r="N218" s="3" t="n"/>
-      <c r="O218" s="3" t="n"/>
+      <c r="J218" s="3" t="n">
+        <v>0.454</v>
+      </c>
+      <c r="K218" s="3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="L218" s="3" t="n">
+        <v>-0.046</v>
+      </c>
+      <c r="M218" s="3" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="N218" s="3" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="O218" s="3" t="n">
+        <v>-0.067</v>
+      </c>
       <c r="P218" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q218" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q218" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -14598,16 +15620,30 @@
       <c r="I219" s="3" t="n">
         <v>0.315</v>
       </c>
-      <c r="J219" s="3" t="n"/>
-      <c r="K219" s="3" t="n"/>
-      <c r="L219" s="3" t="n"/>
-      <c r="M219" s="3" t="n"/>
-      <c r="N219" s="3" t="n"/>
-      <c r="O219" s="3" t="n"/>
+      <c r="J219" s="3" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="K219" s="3" t="n">
+        <v>-0.023</v>
+      </c>
+      <c r="L219" s="3" t="n">
+        <v>-0.043</v>
+      </c>
+      <c r="M219" s="3" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="N219" s="3" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="O219" s="3" t="n">
+        <v>-0.101</v>
+      </c>
       <c r="P219" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q219" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Q219" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">

--- a/research_materials/03_results/serving_precision.xlsx
+++ b/research_materials/03_results/serving_precision.xlsx
@@ -459,7 +459,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Built: 2026-10-07 02:02 by src/build_research_materials.py</t>
+          <t>Built: 2026-10-07 02:47 by src/build_research_materials.py</t>
         </is>
       </c>
     </row>

--- a/research_materials/03_results/serving_precision.xlsx
+++ b/research_materials/03_results/serving_precision.xlsx
@@ -459,7 +459,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Built: 2026-10-07 02:47 by src/build_research_materials.py</t>
+          <t>Built: 2026-10-07 02:57 by src/build_research_materials.py</t>
         </is>
       </c>
     </row>
